--- a/outputs/tables/tab-6-efeitos-marginais.xlsx
+++ b/outputs/tables/tab-6-efeitos-marginais.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -380,6 +380,26 @@
           <t>ame</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ep</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>sup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -403,6 +423,18 @@
       <c r="E2">
         <v>-0.01726203032982156</v>
       </c>
+      <c r="F2">
+        <v>0.002141000349496648</v>
+      </c>
+      <c r="G2">
+        <v>-0.02145831390572266</v>
+      </c>
+      <c r="H2">
+        <v>-0.01306574675392046</v>
+      </c>
+      <c r="I2">
+        <v>7.46883427763991E-16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -426,6 +458,18 @@
       <c r="E3">
         <v>-0.03456458273740905</v>
       </c>
+      <c r="F3">
+        <v>0.003281921609824163</v>
+      </c>
+      <c r="G3">
+        <v>-0.04099703089274813</v>
+      </c>
+      <c r="H3">
+        <v>-0.02813213458206998</v>
+      </c>
+      <c r="I3">
+        <v>6.163614909465015E-26</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -446,6 +490,18 @@
       <c r="E4">
         <v>-0.001185155262962345</v>
       </c>
+      <c r="F4">
+        <v>0.00468088436918508</v>
+      </c>
+      <c r="G4">
+        <v>-0.01035952004236159</v>
+      </c>
+      <c r="H4">
+        <v>0.007989209516436899</v>
+      </c>
+      <c r="I4">
+        <v>0.8001210388203071</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -466,6 +522,18 @@
       <c r="E5">
         <v>-0.01182404051916644</v>
       </c>
+      <c r="F5">
+        <v>0.005467776147393483</v>
+      </c>
+      <c r="G5">
+        <v>-0.02254068484358484</v>
+      </c>
+      <c r="H5">
+        <v>-0.001107396194748049</v>
+      </c>
+      <c r="I5">
+        <v>0.03058001476665245</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -486,6 +554,18 @@
       <c r="E6">
         <v>0.003863110471215421</v>
       </c>
+      <c r="F6">
+        <v>0.00636354763942112</v>
+      </c>
+      <c r="G6">
+        <v>-0.00860921371595485</v>
+      </c>
+      <c r="H6">
+        <v>0.01633543465838569</v>
+      </c>
+      <c r="I6">
+        <v>0.5438053337262683</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -506,6 +586,18 @@
       <c r="E7">
         <v>0.005912458926803791</v>
       </c>
+      <c r="F7">
+        <v>0.006557748576347296</v>
+      </c>
+      <c r="G7">
+        <v>-0.006940492102505719</v>
+      </c>
+      <c r="H7">
+        <v>0.0187654099561133</v>
+      </c>
+      <c r="I7">
+        <v>0.367269973631619</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -529,6 +621,18 @@
       <c r="E8">
         <v>-0.01202052487821336</v>
       </c>
+      <c r="F8">
+        <v>0.003115329441073668</v>
+      </c>
+      <c r="G8">
+        <v>-0.01812645838269505</v>
+      </c>
+      <c r="H8">
+        <v>-0.005914591373731675</v>
+      </c>
+      <c r="I8">
+        <v>0.0001140811383616131</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -549,6 +653,18 @@
       <c r="E9">
         <v>-0.02345212734647337</v>
       </c>
+      <c r="F9">
+        <v>0.007853675956529537</v>
+      </c>
+      <c r="G9">
+        <v>-0.03884504936751942</v>
+      </c>
+      <c r="H9">
+        <v>-0.008059205325427326</v>
+      </c>
+      <c r="I9">
+        <v>0.002825289826559071</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -569,6 +685,18 @@
       <c r="E10">
         <v>0.002543623587085524</v>
       </c>
+      <c r="F10">
+        <v>0.006217668187286101</v>
+      </c>
+      <c r="G10">
+        <v>-0.009642782127815674</v>
+      </c>
+      <c r="H10">
+        <v>0.01473002930198672</v>
+      </c>
+      <c r="I10">
+        <v>0.6824691641227276</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -589,6 +717,18 @@
       <c r="E11">
         <v>-0.02891635967005013</v>
       </c>
+      <c r="F11">
+        <v>0.00726411922643009</v>
+      </c>
+      <c r="G11">
+        <v>-0.04315377173325806</v>
+      </c>
+      <c r="H11">
+        <v>-0.01467894760684219</v>
+      </c>
+      <c r="I11">
+        <v>6.870942984255801E-05</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -609,6 +749,18 @@
       <c r="E12">
         <v>0.02262276899188659</v>
       </c>
+      <c r="F12">
+        <v>0.007199944848013599</v>
+      </c>
+      <c r="G12">
+        <v>0.008511136399105224</v>
+      </c>
+      <c r="H12">
+        <v>0.03673440158466795</v>
+      </c>
+      <c r="I12">
+        <v>0.001677548770577738</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -629,6 +781,18 @@
       <c r="E13">
         <v>-0.02644197455603537</v>
       </c>
+      <c r="F13">
+        <v>0.006941324843474187</v>
+      </c>
+      <c r="G13">
+        <v>-0.0400467212542379</v>
+      </c>
+      <c r="H13">
+        <v>-0.01283722785783284</v>
+      </c>
+      <c r="I13">
+        <v>0.0001393294589154409</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -649,6 +813,18 @@
       <c r="E14">
         <v>0.01537385273991214</v>
       </c>
+      <c r="F14">
+        <v>0.02307169276094069</v>
+      </c>
+      <c r="G14">
+        <v>-0.02984583413390509</v>
+      </c>
+      <c r="H14">
+        <v>0.06059353961372937</v>
+      </c>
+      <c r="I14">
+        <v>0.5051865751485058</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -669,6 +845,18 @@
       <c r="E15">
         <v>-0.02716829202901872</v>
       </c>
+      <c r="F15">
+        <v>0.004895944754324103</v>
+      </c>
+      <c r="G15">
+        <v>-0.03676416741779177</v>
+      </c>
+      <c r="H15">
+        <v>-0.01757241664024568</v>
+      </c>
+      <c r="I15">
+        <v>2.870751593584173E-08</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -692,6 +880,18 @@
       <c r="E16">
         <v>-0.01208155837344638</v>
       </c>
+      <c r="F16">
+        <v>0.002361825404549109</v>
+      </c>
+      <c r="G16">
+        <v>-0.01671065110413437</v>
+      </c>
+      <c r="H16">
+        <v>-0.007452465642758385</v>
+      </c>
+      <c r="I16">
+        <v>3.13163386930874E-07</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -715,6 +915,18 @@
       <c r="E17">
         <v>-0.02865978830930071</v>
       </c>
+      <c r="F17">
+        <v>0.000802497078339037</v>
+      </c>
+      <c r="G17">
+        <v>-0.03023265368054383</v>
+      </c>
+      <c r="H17">
+        <v>-0.02708692293805758</v>
+      </c>
+      <c r="I17">
+        <v>2.461099621076218E-279</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -738,6 +950,18 @@
       <c r="E18">
         <v>-0.02585329181997599</v>
       </c>
+      <c r="F18">
+        <v>0.001572963260004331</v>
+      </c>
+      <c r="G18">
+        <v>-0.02893624315858919</v>
+      </c>
+      <c r="H18">
+        <v>-0.02277034048136279</v>
+      </c>
+      <c r="I18">
+        <v>1.055921970451713E-60</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -758,6 +982,18 @@
       <c r="E19">
         <v>-0.0414520059372924</v>
       </c>
+      <c r="F19">
+        <v>0.001954509576381051</v>
+      </c>
+      <c r="G19">
+        <v>-0.0452827743144379</v>
+      </c>
+      <c r="H19">
+        <v>-0.03762123756014691</v>
+      </c>
+      <c r="I19">
+        <v>7.989730650757931E-100</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -778,6 +1014,18 @@
       <c r="E20">
         <v>-0.02034842603065088</v>
       </c>
+      <c r="F20">
+        <v>0.002464829119766306</v>
+      </c>
+      <c r="G20">
+        <v>-0.0251794023334384</v>
+      </c>
+      <c r="H20">
+        <v>-0.01551744972786336</v>
+      </c>
+      <c r="I20">
+        <v>1.512526046951797E-16</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -798,6 +1046,18 @@
       <c r="E21">
         <v>-0.003000305718813935</v>
       </c>
+      <c r="F21">
+        <v>0.003004840363175065</v>
+      </c>
+      <c r="G21">
+        <v>-0.008889684609929317</v>
+      </c>
+      <c r="H21">
+        <v>0.002889073172301447</v>
+      </c>
+      <c r="I21">
+        <v>0.318041381378048</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -818,6 +1078,18 @@
       <c r="E22">
         <v>-0.004852212729822994</v>
       </c>
+      <c r="F22">
+        <v>0.003038723854666925</v>
+      </c>
+      <c r="G22">
+        <v>-0.01080800204393289</v>
+      </c>
+      <c r="H22">
+        <v>0.001103576584286904</v>
+      </c>
+      <c r="I22">
+        <v>0.110311875183754</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -841,6 +1113,18 @@
       <c r="E23">
         <v>-0.009977771929765273</v>
       </c>
+      <c r="F23">
+        <v>0.001206195228205415</v>
+      </c>
+      <c r="G23">
+        <v>-0.01234187113537196</v>
+      </c>
+      <c r="H23">
+        <v>-0.007613672724158588</v>
+      </c>
+      <c r="I23">
+        <v>1.31615821126104E-16</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -861,6 +1145,18 @@
       <c r="E24">
         <v>-0.04115907494491415</v>
       </c>
+      <c r="F24">
+        <v>0.004315677551348649</v>
+      </c>
+      <c r="G24">
+        <v>-0.04961764751444551</v>
+      </c>
+      <c r="H24">
+        <v>-0.03270050237538279</v>
+      </c>
+      <c r="I24">
+        <v>1.468734676711978E-21</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -881,6 +1177,18 @@
       <c r="E25">
         <v>-0.0168910119337849</v>
       </c>
+      <c r="F25">
+        <v>0.003011707703862944</v>
+      </c>
+      <c r="G25">
+        <v>-0.0227938505653181</v>
+      </c>
+      <c r="H25">
+        <v>-0.01098817330225171</v>
+      </c>
+      <c r="I25">
+        <v>2.04146711402068E-08</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -901,6 +1209,18 @@
       <c r="E26">
         <v>-0.03795255467241975</v>
       </c>
+      <c r="F26">
+        <v>0.003900153290059427</v>
+      </c>
+      <c r="G26">
+        <v>-0.04559671465512163</v>
+      </c>
+      <c r="H26">
+        <v>-0.03030839468971788</v>
+      </c>
+      <c r="I26">
+        <v>2.223043902304409E-22</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -921,6 +1241,18 @@
       <c r="E27">
         <v>0.0161821409677544</v>
       </c>
+      <c r="F27">
+        <v>0.002753839415345631</v>
+      </c>
+      <c r="G27">
+        <v>0.01078471489447012</v>
+      </c>
+      <c r="H27">
+        <v>0.02157956704103867</v>
+      </c>
+      <c r="I27">
+        <v>4.197636878239834E-09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -941,6 +1273,18 @@
       <c r="E28">
         <v>-0.03006615071077639</v>
       </c>
+      <c r="F28">
+        <v>0.003493715529277009</v>
+      </c>
+      <c r="G28">
+        <v>-0.03691370732038762</v>
+      </c>
+      <c r="H28">
+        <v>-0.02321859410116515</v>
+      </c>
+      <c r="I28">
+        <v>7.579886642846677E-18</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -961,6 +1305,18 @@
       <c r="E29">
         <v>-0.003920147624150412</v>
       </c>
+      <c r="F29">
+        <v>0.009492842181619958</v>
+      </c>
+      <c r="G29">
+        <v>-0.02252577641104816</v>
+      </c>
+      <c r="H29">
+        <v>0.01468548116274733</v>
+      </c>
+      <c r="I29">
+        <v>0.6796371925055832</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -981,6 +1337,18 @@
       <c r="E30">
         <v>-0.03852604712588251</v>
       </c>
+      <c r="F30">
+        <v>0.002089549941640579</v>
+      </c>
+      <c r="G30">
+        <v>-0.04262148975539581</v>
+      </c>
+      <c r="H30">
+        <v>-0.0344306044963692</v>
+      </c>
+      <c r="I30">
+        <v>6.572737434476394E-76</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1004,6 +1372,18 @@
       <c r="E31">
         <v>-0.02262923140994388</v>
       </c>
+      <c r="F31">
+        <v>0.001096181198086904</v>
+      </c>
+      <c r="G31">
+        <v>-0.02477770707872418</v>
+      </c>
+      <c r="H31">
+        <v>-0.02048075574116359</v>
+      </c>
+      <c r="I31">
+        <v>1.112235872860596E-94</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1027,6 +1407,18 @@
       <c r="E32">
         <v>-0.02802131229466051</v>
       </c>
+      <c r="F32">
+        <v>0.000803605074868569</v>
+      </c>
+      <c r="G32">
+        <v>-0.02959634929919652</v>
+      </c>
+      <c r="H32">
+        <v>-0.0264462752901245</v>
+      </c>
+      <c r="I32">
+        <v>2.155821611643837E-266</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1050,6 +1442,18 @@
       <c r="E33">
         <v>-0.02867424707739078</v>
       </c>
+      <c r="F33">
+        <v>0.001574587271707177</v>
+      </c>
+      <c r="G33">
+        <v>-0.03176038142045203</v>
+      </c>
+      <c r="H33">
+        <v>-0.02558811273432953</v>
+      </c>
+      <c r="I33">
+        <v>4.24924966799867E-74</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1070,6 +1474,18 @@
       <c r="E34">
         <v>-0.0313074087174389</v>
       </c>
+      <c r="F34">
+        <v>0.002008378571783135</v>
+      </c>
+      <c r="G34">
+        <v>-0.03524375838545584</v>
+      </c>
+      <c r="H34">
+        <v>-0.02737105904942197</v>
+      </c>
+      <c r="I34">
+        <v>8.72924783376824E-55</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1090,6 +1506,18 @@
       <c r="E35">
         <v>-0.01731898820251419</v>
       </c>
+      <c r="F35">
+        <v>0.0024802741594182</v>
+      </c>
+      <c r="G35">
+        <v>-0.02218023622675922</v>
+      </c>
+      <c r="H35">
+        <v>-0.01245774017826916</v>
+      </c>
+      <c r="I35">
+        <v>2.895787449311855E-12</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1110,6 +1538,18 @@
       <c r="E36">
         <v>-0.00277650511025689</v>
       </c>
+      <c r="F36">
+        <v>0.002965053942421944</v>
+      </c>
+      <c r="G36">
+        <v>-0.008587904049622399</v>
+      </c>
+      <c r="H36">
+        <v>0.003034893829108618</v>
+      </c>
+      <c r="I36">
+        <v>0.3490623138058166</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1130,6 +1570,18 @@
       <c r="E37">
         <v>-0.003967899719501004</v>
       </c>
+      <c r="F37">
+        <v>0.003001269763441842</v>
+      </c>
+      <c r="G37">
+        <v>-0.009850280363736062</v>
+      </c>
+      <c r="H37">
+        <v>0.001914480924734053</v>
+      </c>
+      <c r="I37">
+        <v>0.1861436217607504</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1151,7 +1603,19 @@
         <v>2.31866918206821</v>
       </c>
       <c r="E38">
-        <v>-0.007670062167257198</v>
+        <v>-0.007670062167257197</v>
+      </c>
+      <c r="F38">
+        <v>0.001216561159271397</v>
+      </c>
+      <c r="G38">
+        <v>-0.01005447822441943</v>
+      </c>
+      <c r="H38">
+        <v>-0.005285646110094962</v>
+      </c>
+      <c r="I38">
+        <v>2.887388090304256E-10</v>
       </c>
     </row>
     <row r="39">
@@ -1173,6 +1637,18 @@
       <c r="E39">
         <v>-0.03725758008598374</v>
       </c>
+      <c r="F39">
+        <v>0.004398177180414252</v>
+      </c>
+      <c r="G39">
+        <v>-0.04587784895722159</v>
+      </c>
+      <c r="H39">
+        <v>-0.02863731121474589</v>
+      </c>
+      <c r="I39">
+        <v>2.430003792172487E-17</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1193,6 +1669,18 @@
       <c r="E40">
         <v>-0.01250635908897402</v>
       </c>
+      <c r="F40">
+        <v>0.003062505121308236</v>
+      </c>
+      <c r="G40">
+        <v>-0.01850875882920763</v>
+      </c>
+      <c r="H40">
+        <v>-0.006503959348740408</v>
+      </c>
+      <c r="I40">
+        <v>4.432381490610343E-05</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1213,6 +1701,18 @@
       <c r="E41">
         <v>-0.03284680653529708</v>
       </c>
+      <c r="F41">
+        <v>0.004000475186033707</v>
+      </c>
+      <c r="G41">
+        <v>-0.04068759382096931</v>
+      </c>
+      <c r="H41">
+        <v>-0.02500601924962484</v>
+      </c>
+      <c r="I41">
+        <v>2.198546530451499E-16</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1233,6 +1733,18 @@
       <c r="E42">
         <v>0.0175273122808279</v>
       </c>
+      <c r="F42">
+        <v>0.002718425895515355</v>
+      </c>
+      <c r="G42">
+        <v>0.01219929543097676</v>
+      </c>
+      <c r="H42">
+        <v>0.02285532913067904</v>
+      </c>
+      <c r="I42">
+        <v>1.136380955678601E-10</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1253,6 +1765,18 @@
       <c r="E43">
         <v>-0.02225861624900382</v>
       </c>
+      <c r="F43">
+        <v>0.003647363606495838</v>
+      </c>
+      <c r="G43">
+        <v>-0.02940731755625779</v>
+      </c>
+      <c r="H43">
+        <v>-0.01510991494174986</v>
+      </c>
+      <c r="I43">
+        <v>1.043182652174494E-09</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1273,6 +1797,18 @@
       <c r="E44">
         <v>-0.003618501551424021</v>
       </c>
+      <c r="F44">
+        <v>0.009321356137617224</v>
+      </c>
+      <c r="G44">
+        <v>-0.02188802386822516</v>
+      </c>
+      <c r="H44">
+        <v>0.01465102076537712</v>
+      </c>
+      <c r="I44">
+        <v>0.6978719151819541</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1293,6 +1829,18 @@
       <c r="E45">
         <v>-0.03064244298463282</v>
       </c>
+      <c r="F45">
+        <v>0.002161590104932633</v>
+      </c>
+      <c r="G45">
+        <v>-0.03487908173963894</v>
+      </c>
+      <c r="H45">
+        <v>-0.0264058042296267</v>
+      </c>
+      <c r="I45">
+        <v>1.29212264148207E-45</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1316,6 +1864,18 @@
       <c r="E46">
         <v>-0.01892760630471344</v>
       </c>
+      <c r="F46">
+        <v>0.001160272293874659</v>
+      </c>
+      <c r="G46">
+        <v>-0.02120169821296745</v>
+      </c>
+      <c r="H46">
+        <v>-0.01665351439645944</v>
+      </c>
+      <c r="I46">
+        <v>7.968159697408711E-60</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1336,6 +1896,18 @@
       <c r="E47">
         <v>0.03511079359894648</v>
       </c>
+      <c r="F47">
+        <v>0.009589225404193292</v>
+      </c>
+      <c r="G47">
+        <v>0.0163162571670911</v>
+      </c>
+      <c r="H47">
+        <v>0.05390533003080188</v>
+      </c>
+      <c r="I47">
+        <v>0.0002507587069122343</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1356,6 +1928,18 @@
       <c r="E48">
         <v>0.04068669466562336</v>
       </c>
+      <c r="F48">
+        <v>0.004524820072644879</v>
+      </c>
+      <c r="G48">
+        <v>0.03181821028671549</v>
+      </c>
+      <c r="H48">
+        <v>0.04955517904453124</v>
+      </c>
+      <c r="I48">
+        <v>2.430098346385057E-19</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1376,6 +1960,18 @@
       <c r="E49">
         <v>-0.04300202028132414</v>
       </c>
+      <c r="F49">
+        <v>0.004508292794798772</v>
+      </c>
+      <c r="G49">
+        <v>-0.05183811179089115</v>
+      </c>
+      <c r="H49">
+        <v>-0.03416592877175713</v>
+      </c>
+      <c r="I49">
+        <v>1.450155578330586E-21</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1396,6 +1992,18 @@
       <c r="E50">
         <v>-0.01638517757669806</v>
       </c>
+      <c r="F50">
+        <v>0.004642583362912374</v>
+      </c>
+      <c r="G50">
+        <v>-0.02548447376323116</v>
+      </c>
+      <c r="H50">
+        <v>-0.007285881390164962</v>
+      </c>
+      <c r="I50">
+        <v>0.0004166238418871921</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1416,6 +2024,18 @@
       <c r="E51">
         <v>-0.06548652977265777</v>
       </c>
+      <c r="F51">
+        <v>0.004248163537160773</v>
+      </c>
+      <c r="G51">
+        <v>-0.07381277730592917</v>
+      </c>
+      <c r="H51">
+        <v>-0.05716028223938638</v>
+      </c>
+      <c r="I51">
+        <v>1.292570011982373E-53</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1436,6 +2056,18 @@
       <c r="E52">
         <v>-0.03840906862549075</v>
       </c>
+      <c r="F52">
+        <v>0.004452628672100127</v>
+      </c>
+      <c r="G52">
+        <v>-0.0471360604593374</v>
+      </c>
+      <c r="H52">
+        <v>-0.02968207679164409</v>
+      </c>
+      <c r="I52">
+        <v>6.344857553217024E-18</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1456,6 +2088,18 @@
       <c r="E53">
         <v>-0.08191930874495092</v>
       </c>
+      <c r="F53">
+        <v>0.005270045344360187</v>
+      </c>
+      <c r="G53">
+        <v>-0.09224840781678986</v>
+      </c>
+      <c r="H53">
+        <v>-0.07159020967311197</v>
+      </c>
+      <c r="I53">
+        <v>1.738388483690285E-54</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1475,6 +2119,18 @@
       </c>
       <c r="E54">
         <v>-0.07947593799254443</v>
+      </c>
+      <c r="F54">
+        <v>0.004077142226546838</v>
+      </c>
+      <c r="G54">
+        <v>-0.08746698991642368</v>
+      </c>
+      <c r="H54">
+        <v>-0.07148488606866518</v>
+      </c>
+      <c r="I54">
+        <v>1.257569973237431E-84</v>
       </c>
     </row>
   </sheetData>
